--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_03-11-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£9.94</t>
+          <t>£9.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -810,7 +810,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£14.57</t>
+          <t>£14.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£18.87</t>
+          <t>£18.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£20.62</t>
+          <t>£20.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£20.82</t>
+          <t>£20.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£25.47</t>
+          <t>£25.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£25.32</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£33.29</t>
+          <t>£33.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£31.23</t>
+          <t>£30.82</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£38.33</t>
+          <t>£38.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.48</t>
+          <t>£38.22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£37.84</t>
+          <t>£37.74</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>£1029.48</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2571,17 +2571,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£28.15</t>
+          <t>£28.10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£28.15</t>
+          <t>£28.10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£28.15</t>
+          <t>£28.10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2692,17 +2692,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£34.05</t>
+          <t>£33.94</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£34.05</t>
+          <t>£33.94</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£34.05</t>
+          <t>£33.94</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£34.29</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£37.00</t>
+          <t>£36.80</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£37.00</t>
+          <t>£36.80</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£37.00</t>
+          <t>£36.80</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2934,17 +2934,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£42.20</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£42.20</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£42.20</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a7d0e8e5+80021]
-	GetHandleVerifier [0x0x7ff7a7d0e940+80112]
-	(No symbol) [0x0x7ff7a7a9060f]
-	(No symbol) [0x0x7ff7a7ae8854]
-	(No symbol) [0x0x7ff7a7ae8b1c]
-	(No symbol) [0x0x7ff7a7b3c927]
-	(No symbol) [0x0x7ff7a7b1126f]
-	(No symbol) [0x0x7ff7a7b3968a]
-	(No symbol) [0x0x7ff7a7b11003]
-	(No symbol) [0x0x7ff7a7ad95d1]
-	(No symbol) [0x0x7ff7a7ada3f3]
-	GetHandleVerifier [0x0x7ff7a7fcdc7d+2960429]
-	GetHandleVerifier [0x0x7ff7a7fc7f3a+2936554]
-	GetHandleVerifier [0x0x7ff7a7fe8977+3070247]
-	GetHandleVerifier [0x0x7ff7a7d283ce+185214]
-	GetHandleVerifier [0x0x7ff7a7d2fe1f+216527]
-	GetHandleVerifier [0x0x7ff7a7d17b24+117460]
-	GetHandleVerifier [0x0x7ff7a7d17cdf+117903]
-	GetHandleVerifier [0x0x7ff7a7cfdbb8+11112]
+	GetHandleVerifier [0x0x7ff7c438e8e5+80021]
+	GetHandleVerifier [0x0x7ff7c438e940+80112]
+	(No symbol) [0x0x7ff7c411060f]
+	(No symbol) [0x0x7ff7c4168854]
+	(No symbol) [0x0x7ff7c4168b1c]
+	(No symbol) [0x0x7ff7c41bc927]
+	(No symbol) [0x0x7ff7c419126f]
+	(No symbol) [0x0x7ff7c41b968a]
+	(No symbol) [0x0x7ff7c4191003]
+	(No symbol) [0x0x7ff7c41595d1]
+	(No symbol) [0x0x7ff7c415a3f3]
+	GetHandleVerifier [0x0x7ff7c464dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7c4647f3a+2936554]
+	GetHandleVerifier [0x0x7ff7c4668977+3070247]
+	GetHandleVerifier [0x0x7ff7c43a83ce+185214]
+	GetHandleVerifier [0x0x7ff7c43afe1f+216527]
+	GetHandleVerifier [0x0x7ff7c4397b24+117460]
+	GetHandleVerifier [0x0x7ff7c4397cdf+117903]
+	GetHandleVerifier [0x0x7ff7c437dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
